--- a/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week04_21Sep.xlsx
+++ b/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week04_21Sep.xlsx
@@ -1073,7 +1073,7 @@
     <row r="8" ht="45.75" customHeight="1" s="42">
       <c r="A8" s="50" t="inlineStr">
         <is>
-          <t>SMSC/BV this week: International Day of Peace (Mon 21 Sep) — whole-school reflection + calm tutor-time minute.  European Day of Languages Sat 26 Sep — 'hello' language-taster starter Fri.  PSHE rule-of-law panel links the BV assembly.  EVIDENCE: assembly print + EFL: community → SMSC Evidence Tracker.</t>
+          <t>SMSC/BV this week: International Day of Peace (Mon 21 Sep) — whole-school reflection + calm tutor-time minute.  European Day of Languages Sat 26 Sep — 'hello' language-taster starter Fri.  PSHE rule-of-law panel links the BV assembly.  EVIDENCE: assembly print + evidence platform: community → SMSC Evidence Tracker.</t>
         </is>
       </c>
       <c r="B8" s="51" t="n"/>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="I12" s="56" t="inlineStr">
         <is>
-          <t>TA holds the hoops and prompts 'hard bit — inside or outside?'. Teacher lets every pupil handle every model. LOOP [Feedback Policy]: Voice = sort/handle/say the group [VF, ?] → Audience: name which hoop and why; [R] once received → EVIDENCE: hoop-sort photo, upload same day [E: science — daily EFL; banks ELC 8939].</t>
+          <t>TA holds the hoops and prompts 'hard bit — inside or outside?'. Teacher lets every pupil handle every model. LOOP [Feedback Policy]: Voice = sort/handle/say the group [VF, ?] → Audience: name which hoop and why; [R] once received → EVIDENCE: hoop-sort photo, upload same day [E: science — daily evidence platform; banks ELC 8939].</t>
         </is>
       </c>
       <c r="J12" s="56" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="I13" s="58" t="inlineStr">
         <is>
-          <t>TA sits on the panel and keeps deliberation concrete.  LOOP [Feedback Policy]: Voice = verdict/walk/show-me [VF] → Audience: name the rule-vs-law call back; [R] once used for real → EVIDENCE: verdict photos, same day [E: BV rule of law — daily EFL; banks AQA UAS].</t>
+          <t>TA sits on the panel and keeps deliberation concrete.  LOOP [Feedback Policy]: Voice = verdict/walk/show-me [VF] → Audience: name the rule-vs-law call back; [R] once used for real → EVIDENCE: verdict photos, same day [E: BV rule of law — daily evidence platform; banks AQA UAS].</t>
         </is>
       </c>
       <c r="J13" s="58" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="I14" s="56" t="inlineStr">
         <is>
-          <t>TA runs the dreidel table and records voice-notes.  LOOP [Feedback Policy]: Voice = add-a-candle/play/voice-note [VF] → Audience: listen fully before tagging, then [R] → EVIDENCE: make photo + voice-note, same day [E: cultural — daily EFL].</t>
+          <t>TA runs the dreidel table and records voice-notes.  LOOP [Feedback Policy]: Voice = add-a-candle/play/voice-note [VF] → Audience: listen fully before tagging, then [R] → EVIDENCE: make photo + voice-note, same day [E: cultural — daily evidence platform].</t>
         </is>
       </c>
       <c r="J14" s="56" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="I15" s="56" t="inlineStr">
         <is>
-          <t>TA builds alongside and scribes the 'important because' line.  LOOP [Feedback Policy]: Voice = choose/stick/say [VF, ?] → Audience: name the achievement back; [R] once received → EVIDENCE: card + wall photo, same day [E: humanities/BHM — daily EFL; banks AQA UAS].</t>
+          <t>TA builds alongside and scribes the 'important because' line.  LOOP [Feedback Policy]: Voice = choose/stick/say [VF, ?] → Audience: name the achievement back; [R] once received → EVIDENCE: card + wall photo, same day [E: humanities/BHM — daily evidence platform; banks AQA UAS].</t>
         </is>
       </c>
       <c r="J15" s="56" t="inlineStr">
